--- a/data/supporting_tables/s3.xlsx
+++ b/data/supporting_tables/s3.xlsx
@@ -2206,9 +2206,7 @@
       <c r="H35" s="2">
         <v>1</v>
       </c>
-      <c r="I35" s="2">
-        <v>0.9</v>
-      </c>
+      <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="1" t="s">
         <v>16</v>
@@ -3165,7 +3163,7 @@
         <v>53</v>
       </c>
       <c r="E65" s="2">
-        <v>80</v>
+        <v>0.8</v>
       </c>
       <c r="F65" s="2">
         <v>0.8</v>
